--- a/output/個人情報使用同意書_いいかいご.xlsx
+++ b/output/個人情報使用同意書_いいかいご.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>（1）障害福祉/高齢者介護サービスの提供のため</t>
+          <t>（1）介護サービスの提供のため</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>事業所は、障害福祉サービスを円滑に提供するため下記の事業者、機関等へ個人情報を提供することがあります。</t>
+          <t>事業所は、介護サービスを円滑に提供するため下記の事業者、機関等へ個人情報を提供することがあります。</t>
         </is>
       </c>
     </row>
@@ -571,133 +571,125 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>居宅介護・重度訪問介護契約書の第２条に定める契約期間及び法令の定めるところによる当該</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>契約の解約又は解除後の書類保存期間に相当する期間使用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+          <t>指定訪問介護契約書の第２条に定める契約期間、及び法令の定めるところによる当該契約の解約又は解除後の書類保存期間に相当する期間使用します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　年　　月　　日</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>利用者</t>
         </is>
       </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>（住所）</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr"/>
+          <t>（氏名）</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
+        </is>
+      </c>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="7" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>（氏名）</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>（代理人または立会人等）</t>
         </is>
       </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>（住所）</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>（住所）</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr"/>
+          <t>（氏名）</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
+        </is>
+      </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>（氏名）</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　　　　　　　　印</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="C29:E29"/>
+  <mergeCells count="25">
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
